--- a/sg-rorquestionnaire/ig/StructureDefinition-ror-launchcontext.xlsx
+++ b/sg-rorquestionnaire/ig/StructureDefinition-ror-launchcontext.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-04T17:27:39+00:00</t>
+    <t>2026-02-05T18:16:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/sg-rorquestionnaire/ig/StructureDefinition-ror-launchcontext.xlsx
+++ b/sg-rorquestionnaire/ig/StructureDefinition-ror-launchcontext.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-05T18:16:37+00:00</t>
+    <t>2026-02-06T16:44:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -258,7 +258,7 @@
   </si>
   <si>
     <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-ext-1:Must have either extensions or value[x], not both {extension.exists() != value.exists()}sdc-lcext-1:Types must be from the specified value set of resource types based on name: patient: Patient; user: Patient, Practitioner, PractitionerRole, Organization, RelatedPerson, Device; encounter: Encounter; location: Location; study: ResearchStudy; clinical: Any allowed clinical resource {(extension('name').value.where(code='patient' and system='http://hl7.org/fhir/uv/sdc/CodeSystem/launchContext').exists() implies extension('type').all(value = 'Patient')) and (extension('name').value.where(code='user' and system='http://hl7.org/fhir/uv/sdc/CodeSystem/launchContext').exists() implies extension('type').all(value='Patient' or value='Practitioner' or value='PractitionerRole' or value='RelatedPerson' or value='Organization' or value='Device')) and (extension('name').value.where(code='encounter' and system='http://hl7.org/fhir/uv/sdc/CodeSystem/launchContext').exists() implies extension('type').all(value = 'Encounter')) and (extension('name').value.where(code='location' and system='http://hl7.org/fhir/uv/sdc/CodeSystem/launchContext').exists() implies extension('type').all(value = 'Location')) and (extension('name').value.where(code='study' and system='http://hl7.org/fhir/uv/sdc/CodeSystem/launchContext').exists() implies extension('type').all(value = 'ResearchStudy'))}ror-inv-1:Types must be from the specified value set of resource types based on name: patient: Patient; user: Patient, Practitioner, PractitionerRole, Organization, RelatedPerson, Device; encounter: Encounter; location: Location; study: ResearchStudy; clinical: Any allowed clinical resource {(extension('name').value.where(code='patient' and system='http://hl7.org/fhir/uv/sdc/CodeSystem/launchContext').exists() implies extension('type').all(value = 'Patient')) and (extension('name').value.where(code='user' and system='http://hl7.org/fhir/uv/sdc/CodeSystem/launchContext').exists() implies extension('type').all(value='Patient' or value='Practitioner' or value='PractitionerRole' or value='RelatedPerson' or value='Organization' or value='Device')) and (extension('name').value.where(code='encounter' and system='http://hl7.org/fhir/uv/sdc/CodeSystem/launchContext').exists() implies extension('type').all(value = 'Encounter')) and (extension('name').value.where(code='location' and system='http://hl7.org/fhir/uv/sdc/CodeSystem/launchContext').exists() implies extension('type').all(value = 'Location')) and (extension('name').value.where(code='study' and system='http://hl7.org/fhir/uv/sdc/CodeSystem/launchContext').exists() implies extension('type').all(value = 'ResearchStudy'))}</t>
+ext-1:Must have either extensions or value[x], not both {extension.exists() != value.exists()}sdc-lcext-1:Types must be from the specified value set of resource types based on name: patient: Patient; user: Patient, Practitioner, PractitionerRole, Organization, RelatedPerson, Device; encounter: Encounter; location: Location; study: ResearchStudy; clinical: Any allowed clinical resource {(extension('name').value.where(code='patient' and system='http://hl7.org/fhir/uv/sdc/CodeSystem/launchContext').exists() implies extension('type').all(value = 'Patient')) and (extension('name').value.where(code='user' and system='http://hl7.org/fhir/uv/sdc/CodeSystem/launchContext').exists() implies extension('type').all(value='Patient' or value='Practitioner' or value='PractitionerRole' or value='RelatedPerson' or value='Organization' or value='Device')) and (extension('name').value.where(code='encounter' and system='http://hl7.org/fhir/uv/sdc/CodeSystem/launchContext').exists() implies extension('type').all(value = 'Encounter')) and (extension('name').value.where(code='location' and system='http://hl7.org/fhir/uv/sdc/CodeSystem/launchContext').exists() implies extension('type').all(value = 'Location')) and (extension('name').value.where(code='study' and system='http://hl7.org/fhir/uv/sdc/CodeSystem/launchContext').exists() implies extension('type').all(value = 'ResearchStudy'))}ror-inv-1:Types must be from the specified value set of resource types based on name: patient: Patient; user: Patient, Practitioner, PractitionerRole, Organization, RelatedPerson, Device; encounter: Encounter; location: Location; study: ResearchStudy; clinical: Any allowed clinical resource; ror-structure: Location, HealthcareServive, Organization {(extension('name').value.where(code='patient' and system='http://hl7.org/fhir/uv/sdc/CodeSystem/launchContext').exists() implies extension('type').all(value = 'Patient')) and (extension('name').value.where(code='user' and system='http://hl7.org/fhir/uv/sdc/CodeSystem/launchContext').exists() implies extension('type').all(value='Patient' or value='Practitioner' or value='PractitionerRole' or value='RelatedPerson' or value='Organization' or value='Device')) and (extension('name').value.where(code='encounter' and system='http://hl7.org/fhir/uv/sdc/CodeSystem/launchContext').exists() implies extension('type').all(value = 'Encounter')) and (extension('name').value.where(code='location' and system='http://hl7.org/fhir/uv/sdc/CodeSystem/launchContext').exists() implies extension('type').all(value = 'Location')) and (extension('name').value.where(code='study' and system='http://hl7.org/fhir/uv/sdc/CodeSystem/launchContext').exists() implies extension('type').all(value = 'ResearchStudy')) and (extension('name').value.where(code='ror-structure' and system='http://hl7.org/fhir/uv/sdc/CodeSystem/launchContext').exists() implies extension('type').all(value='Location' or value='HealthcareService' or value='Organization'))}</t>
   </si>
   <si>
     <t>Extension.id</t>

--- a/sg-rorquestionnaire/ig/StructureDefinition-ror-launchcontext.xlsx
+++ b/sg-rorquestionnaire/ig/StructureDefinition-ror-launchcontext.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-06T16:44:46+00:00</t>
+    <t>2026-02-09T14:48:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/sg-rorquestionnaire/ig/StructureDefinition-ror-launchcontext.xlsx
+++ b/sg-rorquestionnaire/ig/StructureDefinition-ror-launchcontext.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-09T14:48:50+00:00</t>
+    <t>2026-02-13T15:04:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/sg-rorquestionnaire/ig/StructureDefinition-ror-launchcontext.xlsx
+++ b/sg-rorquestionnaire/ig/StructureDefinition-ror-launchcontext.xlsx
@@ -42,7 +42,7 @@
     <t>Title</t>
   </si>
   <si>
-    <t>Profil de LaunchContextExtension créée dans le cadre du ROR afin d'ajouter le name 'structure' acceptant les ressources FHIR 'Organization', 'HealthcareService' et 'Location'</t>
+    <t>Profil de LaunchContextExtension créée dans le cadre du ROR afin d'ajouter le name 'ror-structure' acceptant les ressources FHIR 'Organization', 'HealthcareService' et 'Location'</t>
   </si>
   <si>
     <t>Status</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-13T15:04:48+00:00</t>
+    <t>2026-02-13T15:15:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/sg-rorquestionnaire/ig/StructureDefinition-ror-launchcontext.xlsx
+++ b/sg-rorquestionnaire/ig/StructureDefinition-ror-launchcontext.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-13T15:15:54+00:00</t>
+    <t>2026-02-13T15:40:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/sg-rorquestionnaire/ig/StructureDefinition-ror-launchcontext.xlsx
+++ b/sg-rorquestionnaire/ig/StructureDefinition-ror-launchcontext.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-13T15:40:14+00:00</t>
+    <t>2026-02-13T15:51:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/sg-rorquestionnaire/ig/StructureDefinition-ror-launchcontext.xlsx
+++ b/sg-rorquestionnaire/ig/StructureDefinition-ror-launchcontext.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-13T15:51:32+00:00</t>
+    <t>2026-02-17T13:15:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/sg-rorquestionnaire/ig/StructureDefinition-ror-launchcontext.xlsx
+++ b/sg-rorquestionnaire/ig/StructureDefinition-ror-launchcontext.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-17T13:15:51+00:00</t>
+    <t>2026-02-18T14:12:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -258,7 +258,7 @@
   </si>
   <si>
     <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-ext-1:Must have either extensions or value[x], not both {extension.exists() != value.exists()}sdc-lcext-1:Types must be from the specified value set of resource types based on name: patient: Patient; user: Patient, Practitioner, PractitionerRole, Organization, RelatedPerson, Device; encounter: Encounter; location: Location; study: ResearchStudy; clinical: Any allowed clinical resource {(extension('name').value.where(code='patient' and system='http://hl7.org/fhir/uv/sdc/CodeSystem/launchContext').exists() implies extension('type').all(value = 'Patient')) and (extension('name').value.where(code='user' and system='http://hl7.org/fhir/uv/sdc/CodeSystem/launchContext').exists() implies extension('type').all(value='Patient' or value='Practitioner' or value='PractitionerRole' or value='RelatedPerson' or value='Organization' or value='Device')) and (extension('name').value.where(code='encounter' and system='http://hl7.org/fhir/uv/sdc/CodeSystem/launchContext').exists() implies extension('type').all(value = 'Encounter')) and (extension('name').value.where(code='location' and system='http://hl7.org/fhir/uv/sdc/CodeSystem/launchContext').exists() implies extension('type').all(value = 'Location')) and (extension('name').value.where(code='study' and system='http://hl7.org/fhir/uv/sdc/CodeSystem/launchContext').exists() implies extension('type').all(value = 'ResearchStudy'))}ror-inv-1:Types must be from the specified value set of resource types based on name: patient: Patient; user: Patient, Practitioner, PractitionerRole, Organization, RelatedPerson, Device; encounter: Encounter; location: Location; study: ResearchStudy; clinical: Any allowed clinical resource; ror-structure: Location, HealthcareServive, Organization {(extension('name').value.where(code='patient' and system='http://hl7.org/fhir/uv/sdc/CodeSystem/launchContext').exists() implies extension('type').all(value = 'Patient')) and (extension('name').value.where(code='user' and system='http://hl7.org/fhir/uv/sdc/CodeSystem/launchContext').exists() implies extension('type').all(value='Patient' or value='Practitioner' or value='PractitionerRole' or value='RelatedPerson' or value='Organization' or value='Device')) and (extension('name').value.where(code='encounter' and system='http://hl7.org/fhir/uv/sdc/CodeSystem/launchContext').exists() implies extension('type').all(value = 'Encounter')) and (extension('name').value.where(code='location' and system='http://hl7.org/fhir/uv/sdc/CodeSystem/launchContext').exists() implies extension('type').all(value = 'Location')) and (extension('name').value.where(code='study' and system='http://hl7.org/fhir/uv/sdc/CodeSystem/launchContext').exists() implies extension('type').all(value = 'ResearchStudy')) and (extension('name').value.where(code='ror-structure' and system='http://hl7.org/fhir/uv/sdc/CodeSystem/launchContext').exists() implies extension('type').all(value='Location' or value='HealthcareService' or value='Organization'))}</t>
+ext-1:Must have either extensions or value[x], not both {extension.exists() != value.exists()}sdc-lcext-1:Types must be from the specified value set of resource types based on name: patient: Patient; user: Patient, Practitioner, PractitionerRole, Organization, RelatedPerson, Device; encounter: Encounter; location: Location; study: ResearchStudy; clinical: Any allowed clinical resource {(extension('name').value.where(code='patient' and system='http://hl7.org/fhir/uv/sdc/CodeSystem/launchContext').exists() implies extension('type').all(value = 'Patient')) and (extension('name').value.where(code='user' and system='http://hl7.org/fhir/uv/sdc/CodeSystem/launchContext').exists() implies extension('type').all(value='Patient' or value='Practitioner' or value='PractitionerRole' or value='RelatedPerson' or value='Organization' or value='Device')) and (extension('name').value.where(code='encounter' and system='http://hl7.org/fhir/uv/sdc/CodeSystem/launchContext').exists() implies extension('type').all(value = 'Encounter')) and (extension('name').value.where(code='location' and system='http://hl7.org/fhir/uv/sdc/CodeSystem/launchContext').exists() implies extension('type').all(value = 'Location')) and (extension('name').value.where(code='study' and system='http://hl7.org/fhir/uv/sdc/CodeSystem/launchContext').exists() implies extension('type').all(value = 'ResearchStudy'))}ror-inv-1:Types must be from the specified value set of resource types based on name ror-structure: Location, HealthcareServive, Organization {(extension('name').value.where(code='ror-structure' and system='http://hl7.org/fhir/uv/sdc/CodeSystem/launchContext').exists() implies extension('type').all(value='Location' or value='HealthcareService' or value='Organization'))}</t>
   </si>
   <si>
     <t>Extension.id</t>

--- a/sg-rorquestionnaire/ig/StructureDefinition-ror-launchcontext.xlsx
+++ b/sg-rorquestionnaire/ig/StructureDefinition-ror-launchcontext.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="881" uniqueCount="148">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1112" uniqueCount="159">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-18T14:12:10+00:00</t>
+    <t>2026-02-18T14:26:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -258,7 +258,7 @@
   </si>
   <si>
     <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-ext-1:Must have either extensions or value[x], not both {extension.exists() != value.exists()}sdc-lcext-1:Types must be from the specified value set of resource types based on name: patient: Patient; user: Patient, Practitioner, PractitionerRole, Organization, RelatedPerson, Device; encounter: Encounter; location: Location; study: ResearchStudy; clinical: Any allowed clinical resource {(extension('name').value.where(code='patient' and system='http://hl7.org/fhir/uv/sdc/CodeSystem/launchContext').exists() implies extension('type').all(value = 'Patient')) and (extension('name').value.where(code='user' and system='http://hl7.org/fhir/uv/sdc/CodeSystem/launchContext').exists() implies extension('type').all(value='Patient' or value='Practitioner' or value='PractitionerRole' or value='RelatedPerson' or value='Organization' or value='Device')) and (extension('name').value.where(code='encounter' and system='http://hl7.org/fhir/uv/sdc/CodeSystem/launchContext').exists() implies extension('type').all(value = 'Encounter')) and (extension('name').value.where(code='location' and system='http://hl7.org/fhir/uv/sdc/CodeSystem/launchContext').exists() implies extension('type').all(value = 'Location')) and (extension('name').value.where(code='study' and system='http://hl7.org/fhir/uv/sdc/CodeSystem/launchContext').exists() implies extension('type').all(value = 'ResearchStudy'))}ror-inv-1:Types must be from the specified value set of resource types based on name ror-structure: Location, HealthcareServive, Organization {(extension('name').value.where(code='ror-structure' and system='http://hl7.org/fhir/uv/sdc/CodeSystem/launchContext').exists() implies extension('type').all(value='Location' or value='HealthcareService' or value='Organization'))}</t>
+ext-1:Must have either extensions or value[x], not both {extension.exists() != value.exists()}inv-1:Types must be from the specified value set of resource types based on name: patient: Patient; user: Patient, Practitioner, PractitionerRole, RelatedPerson (could be a subset of these); encounter: Encounter; location: Location; study: ResearchStudy {(extension('name').value.where(code='patient' and system='http://hl7.org/fhir/uv/sdc/CodeSystem/launchContext').exists() implies extension('type').value = 'Patient') and (extension('name').value.where(code='user' and system='http://hl7.org/fhir/uv/sdc/CodeSystem/launchContext').exists() implies (extension('type').value='Patient' or extension('type').value='Practitioner' or extension('type').value='PractitionerRole' or extension('type').value='RelatedPerson')) and (extension('name').value.where(code='encounter' and system='http://hl7.org/fhir/uv/sdc/CodeSystem/launchContext').exists() implies extension('type').value = 'Encounter') and (extension('name').value.where(code='location' and system='http://hl7.org/fhir/uv/sdc/CodeSystem/launchContext').exists() implies extension('type').value = 'Location') and (extension('name').value.where(code='study' and system='http://hl7.org/fhir/uv/sdc/CodeSystem/launchContext').exists() implies extension('type').value = 'ResearchStudy')}ror-inv-1:Types must be from the specified value set of resource types based on name ror-structure: Location, HealthcareServive, Organization {(extension('name').value.where(code='ror-structure' and system='http://hl7.org/fhir/uv/sdc/CodeSystem/launchContext').exists() implies extension('type').all(value='Location' or value='HealthcareService' or value='Organization'))}</t>
   </si>
   <si>
     <t>Extension.id</t>
@@ -286,6 +286,10 @@
     <t>Extension.extension</t>
   </si>
   <si>
+    <t>extensions
+user content</t>
+  </si>
+  <si>
     <t>2</t>
   </si>
   <si>
@@ -293,6 +297,15 @@
 </t>
   </si>
   <si>
+    <t>Additional content defined by implementations</t>
+  </si>
+  <si>
+    <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
+  </si>
+  <si>
+    <t>There can be no stigma associated with the use of extensions by any application, project, or standard - regardless of the institution or jurisdiction that uses or defines the extensions.  The use of extensions is what allows the FHIR specification to retain a core level of simplicity for everyone.</t>
+  </si>
+  <si>
     <t xml:space="preserve">value:url}
 </t>
   </si>
@@ -328,10 +341,22 @@
     <t>Extension.extension.extension</t>
   </si>
   <si>
-    <t>Extension.extension:name.url</t>
-  </si>
-  <si>
-    <t>Extension.extension.url</t>
+    <t>Extension.extension:name.extension.id</t>
+  </si>
+  <si>
+    <t>Extension.extension.extension.id</t>
+  </si>
+  <si>
+    <t>Extension.extension:name.extension.extension</t>
+  </si>
+  <si>
+    <t>Extension.extension.extension.extension</t>
+  </si>
+  <si>
+    <t>Extension.extension:name.extension.url</t>
+  </si>
+  <si>
+    <t>Extension.extension.extension.url</t>
   </si>
   <si>
     <t xml:space="preserve">uri
@@ -353,6 +378,35 @@
     <t>N/A</t>
   </si>
   <si>
+    <t>Extension.extension:name.extension.value[x]</t>
+  </si>
+  <si>
+    <t>Extension.extension.extension.value[x]</t>
+  </si>
+  <si>
+    <t>base64Binary
+booleancanonicalcodedatedateTimedecimalidinstantintegermarkdownoidpositiveIntstringtimeunsignedInturiurluuidAddressAgeAnnotationAttachmentCodeableConceptCodingContactPointCountDistanceDurationHumanNameIdentifierMoneyPeriodQuantityRangeRatioReferenceSampledDataSignatureTimingContactDetailContributorDataRequirementExpressionParameterDefinitionRelatedArtifactTriggerDefinitionUsageContextDosageMeta</t>
+  </si>
+  <si>
+    <t>Value of extension</t>
+  </si>
+  <si>
+    <t>Value of extension - must be one of a constrained set of the data types (see [Extensibility](http://hl7.org/fhir/R4/extensibility.html) for a list).</t>
+  </si>
+  <si>
+    <t>Extension.value[x]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+</t>
+  </si>
+  <si>
+    <t>Extension.extension:name.url</t>
+  </si>
+  <si>
+    <t>Extension.extension.url</t>
+  </si>
+  <si>
     <t>Extension.extension:name.value[x]</t>
   </si>
   <si>
@@ -363,25 +417,12 @@
 </t>
   </si>
   <si>
-    <t>Value of extension</t>
-  </si>
-  <si>
-    <t>Value of extension - must be one of a constrained set of the data types (see [Extensibility](http://hl7.org/fhir/R4/extensibility.html) for a list).</t>
-  </si>
-  <si>
     <t>extensible</t>
   </si>
   <si>
     <t>https://interop.esante.gouv.fr/ig/fhir/ror/ValueSet/ror-launch-context-vs</t>
   </si>
   <si>
-    <t>Extension.value[x]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-</t>
-  </si>
-  <si>
     <t>Extension.extension:type</t>
   </si>
   <si>
@@ -398,6 +439,18 @@
   </si>
   <si>
     <t>Extension.extension:type.extension</t>
+  </si>
+  <si>
+    <t>Extension.extension:type.extension.id</t>
+  </si>
+  <si>
+    <t>Extension.extension:type.extension.extension</t>
+  </si>
+  <si>
+    <t>Extension.extension:type.extension.url</t>
+  </si>
+  <si>
+    <t>Extension.extension:type.extension.value[x]</t>
   </si>
   <si>
     <t>Extension.extension:type.url</t>
@@ -434,42 +487,22 @@
     <t>Extension.extension:description.extension</t>
   </si>
   <si>
+    <t>Extension.extension:description.extension.id</t>
+  </si>
+  <si>
+    <t>Extension.extension:description.extension.extension</t>
+  </si>
+  <si>
+    <t>Extension.extension:description.extension.url</t>
+  </si>
+  <si>
+    <t>Extension.extension:description.extension.value[x]</t>
+  </si>
+  <si>
     <t>Extension.extension:description.url</t>
   </si>
   <si>
     <t>Extension.extension:description.value[x]</t>
-  </si>
-  <si>
-    <t>Extension.extension:multiplesAllowed</t>
-  </si>
-  <si>
-    <t>multiplesAllowed</t>
-  </si>
-  <si>
-    <t>Allow multiple resources</t>
-  </si>
-  <si>
-    <t>Indicates whether multiple resources are permitted for this context element.</t>
-  </si>
-  <si>
-    <t>Extension.extension:multiplesAllowed.id</t>
-  </si>
-  <si>
-    <t>Extension.extension:multiplesAllowed.extension</t>
-  </si>
-  <si>
-    <t>Extension.extension:multiplesAllowed.url</t>
-  </si>
-  <si>
-    <t>Extension.extension:multiplesAllowed.value[x]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">boolean
-</t>
-  </si>
-  <si>
-    <t>base64Binary
-booleancanonicalcodedatedateTimedecimalidinstantintegermarkdownoidpositiveIntstringtimeunsignedInturiurluuidAddressAgeAnnotationAttachmentCodeableConceptCodingContactPointCountDistanceDurationHumanNameIdentifierMoneyPeriodQuantityRangeRatioReferenceSampledDataSignatureTimingContactDetailContributorDataRequirementExpressionParameterDefinitionRelatedArtifactTriggerDefinitionUsageContextDosageMeta</t>
   </si>
 </sst>
 </file>
@@ -771,13 +804,13 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AK26"/>
+  <dimension ref="A1:AK33"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="45.39453125" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="29.1484375" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="16.671875" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="4" max="4" width="8.95703125" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="1" max="1" width="49.51171875" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="38.703125" customWidth="true" bestFit="true"/>
+    <col min="3" max="3" width="12.66015625" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="4" max="4" width="12.64453125" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="6.77734375" customWidth="true" bestFit="true"/>
     <col min="6" max="6" width="4.9453125" customWidth="true" bestFit="true"/>
     <col min="7" max="7" width="5.4296875" customWidth="true" bestFit="true"/>
@@ -1140,11 +1173,11 @@
       </c>
       <c r="C4" s="2"/>
       <c r="D4" t="s" s="2">
-        <v>74</v>
+        <v>89</v>
       </c>
       <c r="E4" s="2"/>
       <c r="F4" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="G4" t="s" s="2">
         <v>76</v>
@@ -1159,15 +1192,17 @@
         <v>74</v>
       </c>
       <c r="K4" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="L4" t="s" s="2">
-        <v>30</v>
+        <v>92</v>
       </c>
       <c r="M4" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="N4" s="2"/>
+        <v>93</v>
+      </c>
+      <c r="N4" t="s" s="2">
+        <v>94</v>
+      </c>
       <c r="O4" s="2"/>
       <c r="P4" t="s" s="2">
         <v>74</v>
@@ -1204,19 +1239,19 @@
         <v>74</v>
       </c>
       <c r="AB4" t="s" s="2">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="AC4" t="s" s="2">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="AD4" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AE4" t="s" s="2">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="AF4" t="s" s="2">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="AG4" t="s" s="2">
         <v>75</v>
@@ -1228,21 +1263,21 @@
         <v>74</v>
       </c>
       <c r="AJ4" t="s" s="2">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="AK4" t="s" s="2">
-        <v>74</v>
+        <v>87</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="B5" t="s" s="2">
         <v>88</v>
       </c>
       <c r="C5" t="s" s="2">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="D5" t="s" s="2">
         <v>74</v>
@@ -1264,7 +1299,7 @@
         <v>74</v>
       </c>
       <c r="K5" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="L5" t="s" s="2">
         <v>30</v>
@@ -1321,7 +1356,7 @@
         <v>74</v>
       </c>
       <c r="AF5" t="s" s="2">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="AG5" t="s" s="2">
         <v>75</v>
@@ -1333,7 +1368,7 @@
         <v>74</v>
       </c>
       <c r="AJ5" t="s" s="2">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="AK5" t="s" s="2">
         <v>74</v>
@@ -1341,10 +1376,10 @@
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" t="s" s="2">
@@ -1444,10 +1479,10 @@
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" t="s" s="2">
@@ -1470,7 +1505,7 @@
         <v>74</v>
       </c>
       <c r="K7" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="L7" t="s" s="2">
         <v>30</v>
@@ -1515,19 +1550,19 @@
         <v>74</v>
       </c>
       <c r="AB7" t="s" s="2">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="AC7" t="s" s="2">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="AD7" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AE7" t="s" s="2">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="AF7" t="s" s="2">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="AG7" t="s" s="2">
         <v>75</v>
@@ -1539,7 +1574,7 @@
         <v>74</v>
       </c>
       <c r="AJ7" t="s" s="2">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="AK7" t="s" s="2">
         <v>74</v>
@@ -1547,10 +1582,10 @@
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" t="s" s="2">
@@ -1558,7 +1593,7 @@
       </c>
       <c r="E8" s="2"/>
       <c r="F8" t="s" s="2">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="G8" t="s" s="2">
         <v>82</v>
@@ -1573,24 +1608,22 @@
         <v>74</v>
       </c>
       <c r="K8" t="s" s="2">
-        <v>104</v>
+        <v>83</v>
       </c>
       <c r="L8" t="s" s="2">
-        <v>105</v>
+        <v>84</v>
       </c>
       <c r="M8" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="N8" t="s" s="2">
-        <v>107</v>
-      </c>
+        <v>85</v>
+      </c>
+      <c r="N8" s="2"/>
       <c r="O8" s="2"/>
       <c r="P8" t="s" s="2">
         <v>74</v>
       </c>
       <c r="Q8" s="2"/>
       <c r="R8" t="s" s="2">
-        <v>97</v>
+        <v>74</v>
       </c>
       <c r="S8" t="s" s="2">
         <v>74</v>
@@ -1632,10 +1665,10 @@
         <v>74</v>
       </c>
       <c r="AF8" t="s" s="2">
-        <v>108</v>
+        <v>86</v>
       </c>
       <c r="AG8" t="s" s="2">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="AH8" t="s" s="2">
         <v>82</v>
@@ -1647,26 +1680,26 @@
         <v>74</v>
       </c>
       <c r="AK8" t="s" s="2">
-        <v>109</v>
+        <v>87</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
-        <v>74</v>
+        <v>89</v>
       </c>
       <c r="E9" s="2"/>
       <c r="F9" t="s" s="2">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="G9" t="s" s="2">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="H9" t="s" s="2">
         <v>74</v>
@@ -1678,15 +1711,17 @@
         <v>74</v>
       </c>
       <c r="K9" t="s" s="2">
-        <v>112</v>
+        <v>91</v>
       </c>
       <c r="L9" t="s" s="2">
-        <v>113</v>
+        <v>92</v>
       </c>
       <c r="M9" t="s" s="2">
-        <v>114</v>
-      </c>
-      <c r="N9" s="2"/>
+        <v>93</v>
+      </c>
+      <c r="N9" t="s" s="2">
+        <v>94</v>
+      </c>
       <c r="O9" s="2"/>
       <c r="P9" t="s" s="2">
         <v>74</v>
@@ -1711,56 +1746,56 @@
         <v>74</v>
       </c>
       <c r="X9" t="s" s="2">
-        <v>115</v>
-      </c>
-      <c r="Y9" s="2"/>
+        <v>74</v>
+      </c>
+      <c r="Y9" t="s" s="2">
+        <v>74</v>
+      </c>
       <c r="Z9" t="s" s="2">
-        <v>116</v>
+        <v>74</v>
       </c>
       <c r="AA9" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AB9" t="s" s="2">
-        <v>74</v>
+        <v>95</v>
       </c>
       <c r="AC9" t="s" s="2">
-        <v>74</v>
+        <v>96</v>
       </c>
       <c r="AD9" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AE9" t="s" s="2">
-        <v>74</v>
+        <v>97</v>
       </c>
       <c r="AF9" t="s" s="2">
-        <v>117</v>
+        <v>98</v>
       </c>
       <c r="AG9" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH9" t="s" s="2">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="AI9" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AJ9" t="s" s="2">
-        <v>118</v>
+        <v>99</v>
       </c>
       <c r="AK9" t="s" s="2">
-        <v>109</v>
+        <v>87</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>119</v>
+        <v>110</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="C10" t="s" s="2">
-        <v>120</v>
-      </c>
+        <v>111</v>
+      </c>
+      <c r="C10" s="2"/>
       <c r="D10" t="s" s="2">
         <v>74</v>
       </c>
@@ -1769,7 +1804,7 @@
         <v>82</v>
       </c>
       <c r="G10" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="H10" t="s" s="2">
         <v>74</v>
@@ -1781,15 +1816,17 @@
         <v>74</v>
       </c>
       <c r="K10" t="s" s="2">
-        <v>90</v>
+        <v>112</v>
       </c>
       <c r="L10" t="s" s="2">
-        <v>121</v>
+        <v>113</v>
       </c>
       <c r="M10" t="s" s="2">
-        <v>122</v>
-      </c>
-      <c r="N10" s="2"/>
+        <v>114</v>
+      </c>
+      <c r="N10" t="s" s="2">
+        <v>115</v>
+      </c>
       <c r="O10" s="2"/>
       <c r="P10" t="s" s="2">
         <v>74</v>
@@ -1838,30 +1875,30 @@
         <v>74</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>94</v>
+        <v>116</v>
       </c>
       <c r="AG10" t="s" s="2">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="AH10" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="AI10" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AJ10" t="s" s="2">
-        <v>95</v>
+        <v>74</v>
       </c>
       <c r="AK10" t="s" s="2">
-        <v>74</v>
+        <v>117</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>99</v>
+        <v>119</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
@@ -1884,13 +1921,13 @@
         <v>74</v>
       </c>
       <c r="K11" t="s" s="2">
-        <v>83</v>
+        <v>120</v>
       </c>
       <c r="L11" t="s" s="2">
-        <v>84</v>
+        <v>121</v>
       </c>
       <c r="M11" t="s" s="2">
-        <v>85</v>
+        <v>122</v>
       </c>
       <c r="N11" s="2"/>
       <c r="O11" s="2"/>
@@ -1941,7 +1978,7 @@
         <v>74</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>86</v>
+        <v>123</v>
       </c>
       <c r="AG11" t="s" s="2">
         <v>75</v>
@@ -1953,18 +1990,18 @@
         <v>74</v>
       </c>
       <c r="AJ11" t="s" s="2">
-        <v>74</v>
+        <v>124</v>
       </c>
       <c r="AK11" t="s" s="2">
-        <v>87</v>
+        <v>117</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>101</v>
+        <v>126</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
@@ -1972,10 +2009,10 @@
       </c>
       <c r="E12" s="2"/>
       <c r="F12" t="s" s="2">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="G12" t="s" s="2">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="H12" t="s" s="2">
         <v>74</v>
@@ -1987,22 +2024,24 @@
         <v>74</v>
       </c>
       <c r="K12" t="s" s="2">
-        <v>90</v>
+        <v>112</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>30</v>
+        <v>113</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="N12" s="2"/>
+        <v>114</v>
+      </c>
+      <c r="N12" t="s" s="2">
+        <v>115</v>
+      </c>
       <c r="O12" s="2"/>
       <c r="P12" t="s" s="2">
         <v>74</v>
       </c>
       <c r="Q12" s="2"/>
       <c r="R12" t="s" s="2">
-        <v>74</v>
+        <v>101</v>
       </c>
       <c r="S12" t="s" s="2">
         <v>74</v>
@@ -2032,42 +2071,42 @@
         <v>74</v>
       </c>
       <c r="AB12" t="s" s="2">
-        <v>91</v>
+        <v>74</v>
       </c>
       <c r="AC12" t="s" s="2">
-        <v>92</v>
+        <v>74</v>
       </c>
       <c r="AD12" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AE12" t="s" s="2">
-        <v>93</v>
+        <v>74</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>94</v>
+        <v>116</v>
       </c>
       <c r="AG12" t="s" s="2">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="AH12" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="AI12" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AJ12" t="s" s="2">
-        <v>95</v>
+        <v>74</v>
       </c>
       <c r="AK12" t="s" s="2">
-        <v>74</v>
+        <v>117</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>103</v>
+        <v>128</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -2090,24 +2129,22 @@
         <v>74</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>104</v>
+        <v>129</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>105</v>
+        <v>121</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="N13" t="s" s="2">
-        <v>107</v>
-      </c>
+        <v>122</v>
+      </c>
+      <c r="N13" s="2"/>
       <c r="O13" s="2"/>
       <c r="P13" t="s" s="2">
         <v>74</v>
       </c>
       <c r="Q13" s="2"/>
       <c r="R13" t="s" s="2">
-        <v>120</v>
+        <v>74</v>
       </c>
       <c r="S13" t="s" s="2">
         <v>74</v>
@@ -2125,13 +2162,11 @@
         <v>74</v>
       </c>
       <c r="X13" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Y13" t="s" s="2">
-        <v>74</v>
-      </c>
+        <v>130</v>
+      </c>
+      <c r="Y13" s="2"/>
       <c r="Z13" t="s" s="2">
-        <v>74</v>
+        <v>131</v>
       </c>
       <c r="AA13" t="s" s="2">
         <v>74</v>
@@ -2149,10 +2184,10 @@
         <v>74</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>108</v>
+        <v>123</v>
       </c>
       <c r="AG13" t="s" s="2">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="AH13" t="s" s="2">
         <v>82</v>
@@ -2161,20 +2196,22 @@
         <v>74</v>
       </c>
       <c r="AJ13" t="s" s="2">
-        <v>74</v>
+        <v>124</v>
       </c>
       <c r="AK13" t="s" s="2">
-        <v>109</v>
+        <v>117</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>126</v>
+        <v>132</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>111</v>
-      </c>
-      <c r="C14" s="2"/>
+        <v>88</v>
+      </c>
+      <c r="C14" t="s" s="2">
+        <v>133</v>
+      </c>
       <c r="D14" t="s" s="2">
         <v>74</v>
       </c>
@@ -2183,7 +2220,7 @@
         <v>82</v>
       </c>
       <c r="G14" t="s" s="2">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="H14" t="s" s="2">
         <v>74</v>
@@ -2195,13 +2232,13 @@
         <v>74</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>127</v>
+        <v>91</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>113</v>
+        <v>134</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>114</v>
+        <v>135</v>
       </c>
       <c r="N14" s="2"/>
       <c r="O14" s="2"/>
@@ -2228,11 +2265,13 @@
         <v>74</v>
       </c>
       <c r="X14" t="s" s="2">
-        <v>128</v>
-      </c>
-      <c r="Y14" s="2"/>
+        <v>74</v>
+      </c>
+      <c r="Y14" t="s" s="2">
+        <v>74</v>
+      </c>
       <c r="Z14" t="s" s="2">
-        <v>129</v>
+        <v>74</v>
       </c>
       <c r="AA14" t="s" s="2">
         <v>74</v>
@@ -2250,34 +2289,32 @@
         <v>74</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>117</v>
+        <v>98</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH14" t="s" s="2">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="AI14" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AJ14" t="s" s="2">
-        <v>118</v>
+        <v>99</v>
       </c>
       <c r="AK14" t="s" s="2">
-        <v>109</v>
+        <v>74</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>130</v>
+        <v>136</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="C15" t="s" s="2">
-        <v>131</v>
-      </c>
+        <v>103</v>
+      </c>
+      <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
         <v>74</v>
       </c>
@@ -2298,13 +2335,13 @@
         <v>74</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>90</v>
+        <v>83</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>132</v>
+        <v>84</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>133</v>
+        <v>85</v>
       </c>
       <c r="N15" s="2"/>
       <c r="O15" s="2"/>
@@ -2355,41 +2392,41 @@
         <v>74</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH15" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="AI15" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AJ15" t="s" s="2">
-        <v>95</v>
+        <v>74</v>
       </c>
       <c r="AK15" t="s" s="2">
-        <v>74</v>
+        <v>87</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>99</v>
+        <v>105</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
-        <v>74</v>
+        <v>89</v>
       </c>
       <c r="E16" s="2"/>
       <c r="F16" t="s" s="2">
         <v>75</v>
       </c>
       <c r="G16" t="s" s="2">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="H16" t="s" s="2">
         <v>74</v>
@@ -2401,15 +2438,17 @@
         <v>74</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>83</v>
+        <v>91</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>84</v>
+        <v>92</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="N16" s="2"/>
+        <v>93</v>
+      </c>
+      <c r="N16" t="s" s="2">
+        <v>94</v>
+      </c>
       <c r="O16" s="2"/>
       <c r="P16" t="s" s="2">
         <v>74</v>
@@ -2446,31 +2485,31 @@
         <v>74</v>
       </c>
       <c r="AB16" t="s" s="2">
-        <v>74</v>
+        <v>95</v>
       </c>
       <c r="AC16" t="s" s="2">
-        <v>74</v>
+        <v>96</v>
       </c>
       <c r="AD16" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AE16" t="s" s="2">
-        <v>74</v>
+        <v>97</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>86</v>
+        <v>98</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH16" t="s" s="2">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="AI16" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AJ16" t="s" s="2">
-        <v>74</v>
+        <v>99</v>
       </c>
       <c r="AK16" t="s" s="2">
         <v>87</v>
@@ -2478,10 +2517,10 @@
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>101</v>
+        <v>107</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -2492,7 +2531,7 @@
         <v>75</v>
       </c>
       <c r="G17" t="s" s="2">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="H17" t="s" s="2">
         <v>74</v>
@@ -2504,13 +2543,13 @@
         <v>74</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>90</v>
+        <v>83</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>30</v>
+        <v>84</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="N17" s="2"/>
       <c r="O17" s="2"/>
@@ -2549,53 +2588,53 @@
         <v>74</v>
       </c>
       <c r="AB17" t="s" s="2">
-        <v>91</v>
+        <v>74</v>
       </c>
       <c r="AC17" t="s" s="2">
-        <v>92</v>
+        <v>74</v>
       </c>
       <c r="AD17" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AE17" t="s" s="2">
-        <v>93</v>
+        <v>74</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH17" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="AI17" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AJ17" t="s" s="2">
-        <v>95</v>
+        <v>74</v>
       </c>
       <c r="AK17" t="s" s="2">
-        <v>74</v>
+        <v>87</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>103</v>
+        <v>109</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
-        <v>74</v>
+        <v>89</v>
       </c>
       <c r="E18" s="2"/>
       <c r="F18" t="s" s="2">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="G18" t="s" s="2">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="H18" t="s" s="2">
         <v>74</v>
@@ -2607,16 +2646,16 @@
         <v>74</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>104</v>
+        <v>91</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>105</v>
+        <v>92</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>106</v>
+        <v>93</v>
       </c>
       <c r="N18" t="s" s="2">
-        <v>107</v>
+        <v>94</v>
       </c>
       <c r="O18" s="2"/>
       <c r="P18" t="s" s="2">
@@ -2624,7 +2663,7 @@
       </c>
       <c r="Q18" s="2"/>
       <c r="R18" t="s" s="2">
-        <v>131</v>
+        <v>74</v>
       </c>
       <c r="S18" t="s" s="2">
         <v>74</v>
@@ -2654,39 +2693,39 @@
         <v>74</v>
       </c>
       <c r="AB18" t="s" s="2">
-        <v>74</v>
+        <v>95</v>
       </c>
       <c r="AC18" t="s" s="2">
-        <v>74</v>
+        <v>96</v>
       </c>
       <c r="AD18" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AE18" t="s" s="2">
-        <v>74</v>
+        <v>97</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>108</v>
+        <v>98</v>
       </c>
       <c r="AG18" t="s" s="2">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="AH18" t="s" s="2">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="AI18" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AJ18" t="s" s="2">
-        <v>74</v>
+        <v>99</v>
       </c>
       <c r="AK18" t="s" s="2">
-        <v>109</v>
+        <v>87</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="B19" t="s" s="2">
         <v>111</v>
@@ -2712,7 +2751,7 @@
         <v>74</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>83</v>
+        <v>112</v>
       </c>
       <c r="L19" t="s" s="2">
         <v>113</v>
@@ -2720,7 +2759,9 @@
       <c r="M19" t="s" s="2">
         <v>114</v>
       </c>
-      <c r="N19" s="2"/>
+      <c r="N19" t="s" s="2">
+        <v>115</v>
+      </c>
       <c r="O19" s="2"/>
       <c r="P19" t="s" s="2">
         <v>74</v>
@@ -2769,34 +2810,32 @@
         <v>74</v>
       </c>
       <c r="AF19" t="s" s="2">
+        <v>116</v>
+      </c>
+      <c r="AG19" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AH19" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AI19" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ19" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK19" t="s" s="2">
         <v>117</v>
-      </c>
-      <c r="AG19" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AH19" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AI19" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AJ19" t="s" s="2">
-        <v>118</v>
-      </c>
-      <c r="AK19" t="s" s="2">
-        <v>109</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="C20" t="s" s="2">
-        <v>139</v>
-      </c>
+        <v>119</v>
+      </c>
+      <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
         <v>74</v>
       </c>
@@ -2817,13 +2856,13 @@
         <v>74</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>90</v>
+        <v>120</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>140</v>
+        <v>121</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>141</v>
+        <v>122</v>
       </c>
       <c r="N20" s="2"/>
       <c r="O20" s="2"/>
@@ -2874,22 +2913,22 @@
         <v>74</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>94</v>
+        <v>123</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH20" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="AI20" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AJ20" t="s" s="2">
-        <v>95</v>
+        <v>124</v>
       </c>
       <c r="AK20" t="s" s="2">
-        <v>74</v>
+        <v>117</v>
       </c>
     </row>
     <row r="21">
@@ -2897,7 +2936,7 @@
         <v>142</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>99</v>
+        <v>126</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -2905,7 +2944,7 @@
       </c>
       <c r="E21" s="2"/>
       <c r="F21" t="s" s="2">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="G21" t="s" s="2">
         <v>82</v>
@@ -2920,22 +2959,24 @@
         <v>74</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>83</v>
+        <v>112</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>84</v>
+        <v>113</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="N21" s="2"/>
+        <v>114</v>
+      </c>
+      <c r="N21" t="s" s="2">
+        <v>115</v>
+      </c>
       <c r="O21" s="2"/>
       <c r="P21" t="s" s="2">
         <v>74</v>
       </c>
       <c r="Q21" s="2"/>
       <c r="R21" t="s" s="2">
-        <v>74</v>
+        <v>133</v>
       </c>
       <c r="S21" t="s" s="2">
         <v>74</v>
@@ -2977,10 +3018,10 @@
         <v>74</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>86</v>
+        <v>116</v>
       </c>
       <c r="AG21" t="s" s="2">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="AH21" t="s" s="2">
         <v>82</v>
@@ -2992,7 +3033,7 @@
         <v>74</v>
       </c>
       <c r="AK21" t="s" s="2">
-        <v>87</v>
+        <v>117</v>
       </c>
     </row>
     <row r="22">
@@ -3000,7 +3041,7 @@
         <v>143</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>101</v>
+        <v>128</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -3008,10 +3049,10 @@
       </c>
       <c r="E22" s="2"/>
       <c r="F22" t="s" s="2">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="G22" t="s" s="2">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="H22" t="s" s="2">
         <v>74</v>
@@ -3023,13 +3064,13 @@
         <v>74</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>90</v>
+        <v>144</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>30</v>
+        <v>121</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>78</v>
+        <v>122</v>
       </c>
       <c r="N22" s="2"/>
       <c r="O22" s="2"/>
@@ -3056,62 +3097,62 @@
         <v>74</v>
       </c>
       <c r="X22" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Y22" t="s" s="2">
-        <v>74</v>
-      </c>
+        <v>145</v>
+      </c>
+      <c r="Y22" s="2"/>
       <c r="Z22" t="s" s="2">
-        <v>74</v>
+        <v>146</v>
       </c>
       <c r="AA22" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AB22" t="s" s="2">
-        <v>91</v>
+        <v>74</v>
       </c>
       <c r="AC22" t="s" s="2">
-        <v>92</v>
+        <v>74</v>
       </c>
       <c r="AD22" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AE22" t="s" s="2">
-        <v>93</v>
+        <v>74</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>94</v>
+        <v>123</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH22" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="AI22" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AJ22" t="s" s="2">
-        <v>95</v>
+        <v>124</v>
       </c>
       <c r="AK22" t="s" s="2">
-        <v>74</v>
+        <v>117</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="C23" s="2"/>
+        <v>88</v>
+      </c>
+      <c r="C23" t="s" s="2">
+        <v>148</v>
+      </c>
       <c r="D23" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E23" s="2"/>
       <c r="F23" t="s" s="2">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="G23" t="s" s="2">
         <v>82</v>
@@ -3126,24 +3167,22 @@
         <v>74</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>104</v>
+        <v>91</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>105</v>
+        <v>149</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="N23" t="s" s="2">
-        <v>107</v>
-      </c>
+        <v>150</v>
+      </c>
+      <c r="N23" s="2"/>
       <c r="O23" s="2"/>
       <c r="P23" t="s" s="2">
         <v>74</v>
       </c>
       <c r="Q23" s="2"/>
       <c r="R23" t="s" s="2">
-        <v>139</v>
+        <v>74</v>
       </c>
       <c r="S23" t="s" s="2">
         <v>74</v>
@@ -3185,30 +3224,30 @@
         <v>74</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>108</v>
+        <v>98</v>
       </c>
       <c r="AG23" t="s" s="2">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="AH23" t="s" s="2">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="AI23" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AJ23" t="s" s="2">
-        <v>74</v>
+        <v>99</v>
       </c>
       <c r="AK23" t="s" s="2">
-        <v>109</v>
+        <v>74</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>145</v>
+        <v>151</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>111</v>
+        <v>103</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -3231,13 +3270,13 @@
         <v>74</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>146</v>
+        <v>83</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>113</v>
+        <v>84</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>114</v>
+        <v>85</v>
       </c>
       <c r="N24" s="2"/>
       <c r="O24" s="2"/>
@@ -3288,7 +3327,7 @@
         <v>74</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>117</v>
+        <v>86</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>75</v>
@@ -3300,29 +3339,29 @@
         <v>74</v>
       </c>
       <c r="AJ24" t="s" s="2">
-        <v>118</v>
+        <v>74</v>
       </c>
       <c r="AK24" t="s" s="2">
-        <v>109</v>
+        <v>87</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>108</v>
+        <v>152</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
-        <v>74</v>
+        <v>89</v>
       </c>
       <c r="E25" s="2"/>
       <c r="F25" t="s" s="2">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="G25" t="s" s="2">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="H25" t="s" s="2">
         <v>74</v>
@@ -3334,16 +3373,16 @@
         <v>74</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>104</v>
+        <v>91</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>105</v>
+        <v>92</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>106</v>
+        <v>93</v>
       </c>
       <c r="N25" t="s" s="2">
-        <v>107</v>
+        <v>94</v>
       </c>
       <c r="O25" s="2"/>
       <c r="P25" t="s" s="2">
@@ -3351,7 +3390,7 @@
       </c>
       <c r="Q25" s="2"/>
       <c r="R25" t="s" s="2">
-        <v>32</v>
+        <v>74</v>
       </c>
       <c r="S25" t="s" s="2">
         <v>74</v>
@@ -3381,42 +3420,42 @@
         <v>74</v>
       </c>
       <c r="AB25" t="s" s="2">
-        <v>74</v>
+        <v>95</v>
       </c>
       <c r="AC25" t="s" s="2">
-        <v>74</v>
+        <v>96</v>
       </c>
       <c r="AD25" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AE25" t="s" s="2">
-        <v>74</v>
+        <v>97</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>108</v>
+        <v>98</v>
       </c>
       <c r="AG25" t="s" s="2">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="AH25" t="s" s="2">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="AI25" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AJ25" t="s" s="2">
-        <v>74</v>
+        <v>99</v>
       </c>
       <c r="AK25" t="s" s="2">
-        <v>109</v>
+        <v>87</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>117</v>
+        <v>153</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>117</v>
+        <v>107</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -3427,7 +3466,7 @@
         <v>75</v>
       </c>
       <c r="G26" t="s" s="2">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="H26" t="s" s="2">
         <v>74</v>
@@ -3439,13 +3478,13 @@
         <v>74</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>147</v>
+        <v>83</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>113</v>
+        <v>84</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>114</v>
+        <v>85</v>
       </c>
       <c r="N26" s="2"/>
       <c r="O26" s="2"/>
@@ -3496,22 +3535,751 @@
         <v>74</v>
       </c>
       <c r="AF26" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="AG26" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AH26" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AI26" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ26" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK26" t="s" s="2">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="s" s="2">
+        <v>154</v>
+      </c>
+      <c r="B27" t="s" s="2">
+        <v>109</v>
+      </c>
+      <c r="C27" s="2"/>
+      <c r="D27" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="E27" s="2"/>
+      <c r="F27" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="G27" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="H27" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I27" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J27" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K27" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="L27" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="M27" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="N27" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="O27" s="2"/>
+      <c r="P27" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q27" s="2"/>
+      <c r="R27" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="S27" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T27" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U27" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V27" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W27" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X27" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y27" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z27" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA27" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB27" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="AC27" t="s" s="2">
+        <v>96</v>
+      </c>
+      <c r="AD27" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE27" t="s" s="2">
+        <v>97</v>
+      </c>
+      <c r="AF27" t="s" s="2">
+        <v>98</v>
+      </c>
+      <c r="AG27" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AH27" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AI27" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ27" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK27" t="s" s="2">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="s" s="2">
+        <v>155</v>
+      </c>
+      <c r="B28" t="s" s="2">
+        <v>111</v>
+      </c>
+      <c r="C28" s="2"/>
+      <c r="D28" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E28" s="2"/>
+      <c r="F28" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="G28" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="H28" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I28" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J28" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K28" t="s" s="2">
+        <v>112</v>
+      </c>
+      <c r="L28" t="s" s="2">
+        <v>113</v>
+      </c>
+      <c r="M28" t="s" s="2">
+        <v>114</v>
+      </c>
+      <c r="N28" t="s" s="2">
+        <v>115</v>
+      </c>
+      <c r="O28" s="2"/>
+      <c r="P28" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q28" s="2"/>
+      <c r="R28" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="S28" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T28" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U28" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V28" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W28" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X28" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y28" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z28" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA28" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB28" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC28" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD28" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE28" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF28" t="s" s="2">
+        <v>116</v>
+      </c>
+      <c r="AG28" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AH28" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AI28" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ28" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK28" t="s" s="2">
         <v>117</v>
       </c>
-      <c r="AG26" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AH26" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AI26" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AJ26" t="s" s="2">
-        <v>118</v>
-      </c>
-      <c r="AK26" t="s" s="2">
-        <v>109</v>
+    </row>
+    <row r="29">
+      <c r="A29" t="s" s="2">
+        <v>156</v>
+      </c>
+      <c r="B29" t="s" s="2">
+        <v>119</v>
+      </c>
+      <c r="C29" s="2"/>
+      <c r="D29" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E29" s="2"/>
+      <c r="F29" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="G29" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="H29" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I29" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J29" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K29" t="s" s="2">
+        <v>120</v>
+      </c>
+      <c r="L29" t="s" s="2">
+        <v>121</v>
+      </c>
+      <c r="M29" t="s" s="2">
+        <v>122</v>
+      </c>
+      <c r="N29" s="2"/>
+      <c r="O29" s="2"/>
+      <c r="P29" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q29" s="2"/>
+      <c r="R29" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="S29" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T29" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U29" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V29" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W29" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X29" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y29" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z29" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA29" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB29" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC29" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD29" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE29" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF29" t="s" s="2">
+        <v>123</v>
+      </c>
+      <c r="AG29" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AH29" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AI29" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ29" t="s" s="2">
+        <v>124</v>
+      </c>
+      <c r="AK29" t="s" s="2">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="s" s="2">
+        <v>157</v>
+      </c>
+      <c r="B30" t="s" s="2">
+        <v>126</v>
+      </c>
+      <c r="C30" s="2"/>
+      <c r="D30" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E30" s="2"/>
+      <c r="F30" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="G30" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="H30" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I30" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J30" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K30" t="s" s="2">
+        <v>112</v>
+      </c>
+      <c r="L30" t="s" s="2">
+        <v>113</v>
+      </c>
+      <c r="M30" t="s" s="2">
+        <v>114</v>
+      </c>
+      <c r="N30" t="s" s="2">
+        <v>115</v>
+      </c>
+      <c r="O30" s="2"/>
+      <c r="P30" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q30" s="2"/>
+      <c r="R30" t="s" s="2">
+        <v>148</v>
+      </c>
+      <c r="S30" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T30" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U30" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V30" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W30" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X30" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y30" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z30" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA30" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB30" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC30" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD30" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE30" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF30" t="s" s="2">
+        <v>116</v>
+      </c>
+      <c r="AG30" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AH30" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AI30" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ30" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK30" t="s" s="2">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="s" s="2">
+        <v>158</v>
+      </c>
+      <c r="B31" t="s" s="2">
+        <v>128</v>
+      </c>
+      <c r="C31" s="2"/>
+      <c r="D31" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E31" s="2"/>
+      <c r="F31" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="G31" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="H31" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I31" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J31" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K31" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="L31" t="s" s="2">
+        <v>121</v>
+      </c>
+      <c r="M31" t="s" s="2">
+        <v>122</v>
+      </c>
+      <c r="N31" s="2"/>
+      <c r="O31" s="2"/>
+      <c r="P31" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q31" s="2"/>
+      <c r="R31" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="S31" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T31" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U31" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V31" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W31" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X31" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y31" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z31" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA31" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB31" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC31" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD31" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE31" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF31" t="s" s="2">
+        <v>123</v>
+      </c>
+      <c r="AG31" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AH31" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AI31" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ31" t="s" s="2">
+        <v>124</v>
+      </c>
+      <c r="AK31" t="s" s="2">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="s" s="2">
+        <v>116</v>
+      </c>
+      <c r="B32" t="s" s="2">
+        <v>116</v>
+      </c>
+      <c r="C32" s="2"/>
+      <c r="D32" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E32" s="2"/>
+      <c r="F32" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="G32" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="H32" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I32" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J32" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K32" t="s" s="2">
+        <v>112</v>
+      </c>
+      <c r="L32" t="s" s="2">
+        <v>113</v>
+      </c>
+      <c r="M32" t="s" s="2">
+        <v>114</v>
+      </c>
+      <c r="N32" t="s" s="2">
+        <v>115</v>
+      </c>
+      <c r="O32" s="2"/>
+      <c r="P32" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q32" s="2"/>
+      <c r="R32" t="s" s="2">
+        <v>32</v>
+      </c>
+      <c r="S32" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T32" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U32" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V32" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W32" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X32" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y32" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z32" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA32" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB32" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC32" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD32" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE32" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF32" t="s" s="2">
+        <v>116</v>
+      </c>
+      <c r="AG32" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AH32" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AI32" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ32" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK32" t="s" s="2">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="s" s="2">
+        <v>123</v>
+      </c>
+      <c r="B33" t="s" s="2">
+        <v>123</v>
+      </c>
+      <c r="C33" s="2"/>
+      <c r="D33" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E33" s="2"/>
+      <c r="F33" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="G33" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="H33" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I33" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J33" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K33" t="s" s="2">
+        <v>120</v>
+      </c>
+      <c r="L33" t="s" s="2">
+        <v>121</v>
+      </c>
+      <c r="M33" t="s" s="2">
+        <v>122</v>
+      </c>
+      <c r="N33" s="2"/>
+      <c r="O33" s="2"/>
+      <c r="P33" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q33" s="2"/>
+      <c r="R33" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="S33" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T33" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U33" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V33" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W33" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X33" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y33" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z33" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA33" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB33" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC33" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD33" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE33" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF33" t="s" s="2">
+        <v>123</v>
+      </c>
+      <c r="AG33" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AH33" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AI33" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ33" t="s" s="2">
+        <v>124</v>
+      </c>
+      <c r="AK33" t="s" s="2">
+        <v>117</v>
       </c>
     </row>
   </sheetData>

--- a/sg-rorquestionnaire/ig/StructureDefinition-ror-launchcontext.xlsx
+++ b/sg-rorquestionnaire/ig/StructureDefinition-ror-launchcontext.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-18T14:26:16+00:00</t>
+    <t>2026-02-18T16:47:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/sg-rorquestionnaire/ig/StructureDefinition-ror-launchcontext.xlsx
+++ b/sg-rorquestionnaire/ig/StructureDefinition-ror-launchcontext.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-18T16:47:38+00:00</t>
+    <t>2026-02-19T09:13:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/sg-rorquestionnaire/ig/StructureDefinition-ror-launchcontext.xlsx
+++ b/sg-rorquestionnaire/ig/StructureDefinition-ror-launchcontext.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-19T09:13:17+00:00</t>
+    <t>2026-03-09T13:55:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/sg-rorquestionnaire/ig/StructureDefinition-ror-launchcontext.xlsx
+++ b/sg-rorquestionnaire/ig/StructureDefinition-ror-launchcontext.xlsx
@@ -42,7 +42,7 @@
     <t>Title</t>
   </si>
   <si>
-    <t>Profil de LaunchContextExtension créée dans le cadre du ROR afin d'ajouter le name 'ror-structure' acceptant les ressources FHIR 'Organization', 'HealthcareService' et 'Location'</t>
+    <t>Profil de LaunchContextExtension créé dans le cadre du ROR afin d'ajouter le name 'ror-structure' acceptant les ressources FHIR 'Organization', 'HealthcareService' et 'Location'</t>
   </si>
   <si>
     <t>Status</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-09T13:55:47+00:00</t>
+    <t>2026-03-09T14:10:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
